--- a/outputs/142-19.xlsx
+++ b/outputs/142-19.xlsx
@@ -232,12 +232,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -433,620 +437,620 @@
   <dimension ref="A1:E82"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.73"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B54" s="0" t="s">
+      <c r="B54" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="B55" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="B61" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B62" s="0" t="s">
+      <c r="B62" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="B63" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B64" s="0" t="s">
+      <c r="B64" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B65" s="0" t="s">
+      <c r="B65" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B66" s="0" t="s">
+      <c r="B66" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B67" s="0" t="s">
+      <c r="B67" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B68" s="0" t="s">
+      <c r="B68" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B69" s="0" t="s">
+      <c r="B69" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B70" s="0" t="s">
+      <c r="B70" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B71" s="0" t="s">
+      <c r="B71" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B72" s="0" t="s">
+      <c r="B72" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B73" s="0" t="s">
+      <c r="B73" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="A74" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B74" s="0" t="s">
+      <c r="B74" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+      <c r="A75" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B75" s="0" t="s">
+      <c r="B75" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+      <c r="A76" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B76" s="0" t="s">
+      <c r="B76" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
+      <c r="A77" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B77" s="0" t="s">
+      <c r="B77" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
+      <c r="A78" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B78" s="0" t="s">
+      <c r="B78" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+      <c r="A79" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B79" s="0" t="s">
+      <c r="B79" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
+      <c r="A80" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B80" s="0" t="s">
+      <c r="B80" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+      <c r="A81" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B81" s="0" t="s">
+      <c r="B81" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+      <c r="A82" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B82" s="0" t="s">
+      <c r="B82" s="1" t="s">
         <v>41</v>
       </c>
     </row>

--- a/outputs/142-19.xlsx
+++ b/outputs/142-19.xlsx
@@ -28,124 +28,124 @@
     <t xml:space="preserve">Name</t>
   </si>
   <si>
+    <t xml:space="preserve">Z 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bob</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strange</t>
+  </si>
+  <si>
     <t xml:space="preserve">A 37</t>
   </si>
   <si>
     <t xml:space="preserve">Best</t>
   </si>
   <si>
+    <t xml:space="preserve">D 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nany</t>
+  </si>
+  <si>
     <t xml:space="preserve">A 50</t>
   </si>
   <si>
     <t xml:space="preserve">Bobby</t>
   </si>
   <si>
-    <t xml:space="preserve">A 55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bob</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C 11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C 14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C 18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D 14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tate</t>
-  </si>
-  <si>
     <t xml:space="preserve">D 7</t>
   </si>
   <si>
     <t xml:space="preserve">Who</t>
   </si>
   <si>
-    <t xml:space="preserve">Z 10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z 11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John</t>
+    <t xml:space="preserve">D 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mary1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bob1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ron1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brave1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strange1</t>
   </si>
   <si>
     <t xml:space="preserve">Best1</t>
   </si>
   <si>
+    <t xml:space="preserve">Tate1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julie1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nany1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bobby1</t>
   </si>
   <si>
-    <t xml:space="preserve">Bob1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strange1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mary1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nany1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ron1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tate1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Who1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z 17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z 18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brave1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z 19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julie1</t>
   </si>
   <si>
     <t xml:space="preserve">Z 14</t>
@@ -566,185 +566,185 @@
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>41</v>
@@ -784,7 +784,7 @@
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>9</v>
@@ -792,7 +792,7 @@
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>11</v>
@@ -808,7 +808,7 @@
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>15</v>
@@ -840,18 +840,18 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -872,183 +872,183 @@
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>41</v>
